--- a/llm_labeling/livecodebench_rating.xlsx
+++ b/llm_labeling/livecodebench_rating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,20 +461,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>harmonic_mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>hm_rank</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>distance</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>distance_rank</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>regression_rank</t>
         </is>
@@ -507,15 +517,21 @@
         <v>0.3150795049253524</v>
       </c>
       <c r="H2" t="n">
+        <v>0.2653421324674153</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
         <v>1.031164444863708</v>
       </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.3484849271398221</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -546,15 +562,21 @@
         <v>0.9293606543829673</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1.002491853906655</v>
       </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -585,15 +607,21 @@
         <v>0.2313038475708429</v>
       </c>
       <c r="H4" t="n">
+        <v>0.03822387591108407</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
         <v>1.244853861250589</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.02379702560117045</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -624,15 +652,21 @@
         <v>0.8199505008388774</v>
       </c>
       <c r="H5" t="n">
+        <v>0.332248772821787</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.8118829553939918</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>1.15639939347689</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -663,15 +697,21 @@
         <v>0.9564302284895483</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4811434499542911</v>
+        <v>0.6744101145909104</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
+        <v>0.4811434499542911</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
         <v>3.156055616651186</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -702,15 +742,21 @@
         <v>0.7832440852444773</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6615195587293723</v>
+        <v>0.5071755352926021</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="n">
+        <v>0.6615195587293723</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
         <v>2.012817298517357</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -741,15 +787,21 @@
         <v>0.9993437366586101</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5208337467874796</v>
+        <v>0.6477495269183687</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
+        <v>0.5208337467874796</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
         <v>3.00747904739766</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -780,15 +832,21 @@
         <v>0.7836746869021529</v>
       </c>
       <c r="H9" t="n">
+        <v>0.1838904654699964</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.9215823360926536</v>
       </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.5593647032610807</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -819,15 +877,21 @@
         <v>0.7696341147694327</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4761087608826097</v>
+        <v>0.6636571105166778</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
+        <v>0.4761087608826097</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
         <v>3.085174042917981</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -858,15 +922,21 @@
         <v>0.1526582179122973</v>
       </c>
       <c r="H11" t="n">
+        <v>0.06546520373302327</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.279214944194033</v>
       </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.03675538556895649</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -897,15 +967,21 @@
         <v>0.8609519497605012</v>
       </c>
       <c r="H12" t="n">
+        <v>0.04068223704167918</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.9889902534335296</v>
       </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
         <v>0.1190721897090103</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -936,15 +1012,21 @@
         <v>0.9931754500551946</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7291986027549195</v>
+        <v>0.4256062477701976</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
       </c>
       <c r="J13" t="n">
+        <v>0.7291986027549195</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
         <v>1.690024479724884</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -975,15 +1057,21 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.201850425154663</v>
       </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
         <v>0.1845496320928293</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1014,15 +1102,21 @@
         <v>0.7423497013387048</v>
       </c>
       <c r="H15" t="n">
+        <v>0.3253580470850611</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.8325381597929106</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>1.065049158365789</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1053,15 +1147,21 @@
         <v>0.8475197675148197</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7042062704199208</v>
+        <v>0.4566300243586108</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>0.7042062704199208</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
         <v>1.770338379757636</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1092,15 +1192,21 @@
         <v>0.67733346733848</v>
       </c>
       <c r="H17" t="n">
+        <v>0.1144401911444948</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.9914736210811701</v>
       </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
         <v>0.287006326071959</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1131,15 +1237,21 @@
         <v>0.7332835738967957</v>
       </c>
       <c r="H18" t="n">
+        <v>0.2432832015411487</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.8948398439931642</v>
       </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
         <v>0.7361478154138901</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1170,15 +1282,21 @@
         <v>0.8776686023858781</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1223313976141219</v>
+        <v>0.9348493139531224</v>
       </c>
       <c r="I19" t="n">
         <v>5</v>
       </c>
       <c r="J19" t="n">
+        <v>0.1223313976141219</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
         <v>5.774857788015439</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1209,15 +1327,21 @@
         <v>0.9925503962122996</v>
       </c>
       <c r="H20" t="n">
+        <v>0.1175951404520131</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
         <v>0.9375295977176368</v>
       </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
         <v>0.3897824283604923</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1248,15 +1372,21 @@
         <v>0.6098792904706269</v>
       </c>
       <c r="H21" t="n">
-        <v>0.701763454293168</v>
+        <v>0.495090101446752</v>
       </c>
       <c r="I21" t="n">
         <v>3</v>
       </c>
       <c r="J21" t="n">
+        <v>0.701763454293168</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
         <v>1.643429949934038</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1287,15 +1417,21 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
+        <v>0.1886792452830188</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
         <v>0.6542162275678458</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1326,15 +1462,21 @@
         <v>0.6830686259389415</v>
       </c>
       <c r="H23" t="n">
+        <v>0.04043346146795833</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
         <v>1.029180672659248</v>
       </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.09672994391294272</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
     </row>
